--- a/testdata/config_platforme.xlsx
+++ b/testdata/config_platforme.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9467"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -74,7 +74,7 @@
     <t>16</t>
   </si>
   <si>
-    <t>rs.nlb.klik.test</t>
+    <t>rs.nlb.klik.uat</t>
   </si>
   <si>
     <t>si.nlb.klik.RootActivity</t>

--- a/testdata/config_platforme.xlsx
+++ b/testdata/config_platforme.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="28800" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -74,7 +74,7 @@
     <t>16</t>
   </si>
   <si>
-    <t>rs.nlb.klik.uat</t>
+    <t>rs.nlb.klik.test</t>
   </si>
   <si>
     <t>si.nlb.klik.RootActivity</t>

--- a/testdata/config_platforme.xlsx
+++ b/testdata/config_platforme.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12240"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -74,7 +74,7 @@
     <t>16</t>
   </si>
   <si>
-    <t>rs.nlb.klik.test</t>
+    <t>rs.nlb.klik.uat</t>
   </si>
   <si>
     <t>si.nlb.klik.RootActivity</t>

--- a/testdata/config_platforme.xlsx
+++ b/testdata/config_platforme.xlsx
@@ -74,7 +74,7 @@
     <t>16</t>
   </si>
   <si>
-    <t>rs.nlb.klik.uat</t>
+    <t>rs.nlb.klik.test</t>
   </si>
   <si>
     <t>si.nlb.klik.RootActivity</t>
@@ -805,22 +805,22 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -836,7 +836,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -2029,13 +2029,13 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2062,13 +2062,13 @@
       <c r="H2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2094,14 +2094,14 @@
       <c r="G3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="6" t="s">
+      <c r="H3" s="4"/>
+      <c r="I3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       <c r="C4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="7">
         <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -2127,14 +2127,14 @@
       <c r="G4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="4" t="s">
+      <c r="H4" s="4"/>
+      <c r="I4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="3" t="s">
         <v>20</v>
       </c>
     </row>
